--- a/ig/test-tabs-svs/ValueSet-jdv-j310-categorie-entite-geographique-exercice-finess.xlsx
+++ b/ig/test-tabs-svs/ValueSet-jdv-j310-categorie-entite-geographique-exercice-finess.xlsx
@@ -9,12 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Exclude #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Expansion Parameters" r:id="rId6" sheetId="4"/>
+    <sheet name="Expansion" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1951" uniqueCount="678">
   <si>
     <t>Property</t>
   </si>
@@ -125,6 +127,1929 @@
   </si>
   <si>
     <t>true</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>used-codesystem</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r397-categorie-entite-geographique-exercice|20260601120000</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Abstract</t>
+  </si>
+  <si>
+    <t>Inactive</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>Aire Station Nomades</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>Alarme Médico-Sociale</t>
+  </si>
+  <si>
+    <t>641</t>
+  </si>
+  <si>
+    <t>Antenne de Pharmacie d'officine</t>
+  </si>
+  <si>
+    <t>165</t>
+  </si>
+  <si>
+    <t>Appartement de Coordination Thérapeutique (A.C.T.)</t>
+  </si>
+  <si>
+    <t>412</t>
+  </si>
+  <si>
+    <t>Appartement Thérapeutique</t>
+  </si>
+  <si>
+    <t>357</t>
+  </si>
+  <si>
+    <t>Association Aide aux Insuffisants Respiratoires</t>
+  </si>
+  <si>
+    <t>366</t>
+  </si>
+  <si>
+    <t>Atelier Thérapeutique</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>Autre Centre d'Accueil</t>
+  </si>
+  <si>
+    <t>698</t>
+  </si>
+  <si>
+    <t>Autre Etablissement Loi Hospitalière</t>
+  </si>
+  <si>
+    <t>612</t>
+  </si>
+  <si>
+    <t>Autre Laboratoire de Biologie Médicale sans FSE</t>
+  </si>
+  <si>
+    <t>393</t>
+  </si>
+  <si>
+    <t>Autre résidence But lucratif pr personnes Âgées</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>Autres lits de l-s</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>Autres lits de m.R.</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>Autres places de l-f.</t>
+  </si>
+  <si>
+    <t>259</t>
+  </si>
+  <si>
+    <t>Autres résidences sociales</t>
+  </si>
+  <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>Banque d'Organes</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>Banque de Sperme</t>
+  </si>
+  <si>
+    <t>221</t>
+  </si>
+  <si>
+    <t>Bureau d'Aide Psychologique Universitaire (B.A.P.U.)</t>
+  </si>
+  <si>
+    <t>413</t>
+  </si>
+  <si>
+    <t>C.E.C.O.S</t>
+  </si>
+  <si>
+    <t>605</t>
+  </si>
+  <si>
+    <t>Cabinet d'Auxiliaires Médicaux</t>
+  </si>
+  <si>
+    <t>602</t>
+  </si>
+  <si>
+    <t>Cabinet de Groupe</t>
+  </si>
+  <si>
+    <t>601</t>
+  </si>
+  <si>
+    <t>Cabinet Libéral Médical</t>
+  </si>
+  <si>
+    <t>443</t>
+  </si>
+  <si>
+    <t>Centre Accueil Demandeurs Asile (C.A.D.A.)</t>
+  </si>
+  <si>
+    <t>190</t>
+  </si>
+  <si>
+    <t>Centre Action Médico-Sociale Précoce (C.A.M.S.P.)</t>
+  </si>
+  <si>
+    <t>369</t>
+  </si>
+  <si>
+    <t>Centre Adaptation Vie Active (C.A.V.A.)</t>
+  </si>
+  <si>
+    <t>414</t>
+  </si>
+  <si>
+    <t>Centre Anti Poison</t>
+  </si>
+  <si>
+    <t>359</t>
+  </si>
+  <si>
+    <t>Centre Circonscription Sanitaire et Sociale</t>
+  </si>
+  <si>
+    <t>328</t>
+  </si>
+  <si>
+    <t>Centre Consultation Soins Dentaire</t>
+  </si>
+  <si>
+    <t>444</t>
+  </si>
+  <si>
+    <t>Centre Crise Accueil Permanent</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>Centre d'Accueil Familial Spécialisé</t>
+  </si>
+  <si>
+    <t>425</t>
+  </si>
+  <si>
+    <t>Centre d'Accueil Thérapeutique à temps partiel (C.A.T.T.P.)</t>
+  </si>
+  <si>
+    <t>419</t>
+  </si>
+  <si>
+    <t>Centre d'Accueil Toxicomanes</t>
+  </si>
+  <si>
+    <t>622</t>
+  </si>
+  <si>
+    <t>Centre d'Appareillage &amp; Prothèse</t>
+  </si>
+  <si>
+    <t>421</t>
+  </si>
+  <si>
+    <t>Centre d'enseignement aux secours d'urgence</t>
+  </si>
+  <si>
+    <t>140</t>
+  </si>
+  <si>
+    <t>Centre d'Entraînement à la Dialyse</t>
+  </si>
+  <si>
+    <t>347</t>
+  </si>
+  <si>
+    <t>Centre d'Examens de Santé</t>
+  </si>
+  <si>
+    <t>294</t>
+  </si>
+  <si>
+    <t>Centre de Consultations Cancer</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>Centre de Convalescence Cure ou Réadaptation</t>
+  </si>
+  <si>
+    <t>162</t>
+  </si>
+  <si>
+    <t>Centre de Cure Ambulatoire en Alcoologie (C.C.A.A.)</t>
+  </si>
+  <si>
+    <t>361</t>
+  </si>
+  <si>
+    <t>Centre de Cure Médicale</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>Centre de dialyse</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
+    <t>Centre de Dialyse et d'entraînement à la Dialyse</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>Centre de Dialyse Périodique</t>
+  </si>
+  <si>
+    <t>435</t>
+  </si>
+  <si>
+    <t>Centre de formation d'aide à domicile</t>
+  </si>
+  <si>
+    <t>281</t>
+  </si>
+  <si>
+    <t>Centre de formation d'aides soignants</t>
+  </si>
+  <si>
+    <t>350</t>
+  </si>
+  <si>
+    <t>Centre de formation d'auxiliaires de puériculture</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>Centre de formation professionnelle de secteur psychiatrique</t>
+  </si>
+  <si>
+    <t>373</t>
+  </si>
+  <si>
+    <t>Centre de formation supérieure des travailleurs sociaux</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>Centre de Jour pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>637</t>
+  </si>
+  <si>
+    <t>Centre de Lutte Antituberculeuse (CLAT)</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>Centre de Lutte Contre Cancer</t>
+  </si>
+  <si>
+    <t>438</t>
+  </si>
+  <si>
+    <t>Centre de Médecine collective</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>Centre de Médecine Sportive</t>
+  </si>
+  <si>
+    <t>269</t>
+  </si>
+  <si>
+    <t>Centre de Médecine Universitaire</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>Centre de Placement Familial Spécialisé</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>Centre de Postcure</t>
+  </si>
+  <si>
+    <t>352</t>
+  </si>
+  <si>
+    <t>Centre de Psychothérapie</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>Centre de Santé</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>Centre de Santé Dentaire</t>
+  </si>
+  <si>
+    <t>649</t>
+  </si>
+  <si>
+    <t>Centre de santé et de médiation en santé sexuelle</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>Centre de Santé Sexuelle</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>Centre de Services pour Associations</t>
+  </si>
+  <si>
+    <t>636</t>
+  </si>
+  <si>
+    <t>Centre de soins et de prévention</t>
+  </si>
+  <si>
+    <t>289</t>
+  </si>
+  <si>
+    <t>Centre de Soins Infirmiers</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>Centre de Soins Médicaux</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>Centre de Soins Spécifiques pour Toxicomanes (C.S.S.T.)</t>
+  </si>
+  <si>
+    <t>645</t>
+  </si>
+  <si>
+    <t>Centre de Vaccination</t>
+  </si>
+  <si>
+    <t>143</t>
+  </si>
+  <si>
+    <t>Centre de Vaccination BCG</t>
+  </si>
+  <si>
+    <t>646</t>
+  </si>
+  <si>
+    <t>Centre de Vaccination Internationale</t>
+  </si>
+  <si>
+    <t>638</t>
+  </si>
+  <si>
+    <t>Centre gratuit d'information de dépistage et de diagnostic (CeGIDD)</t>
+  </si>
+  <si>
+    <t>355</t>
+  </si>
+  <si>
+    <t>Centre Hospitalier (C.H.)</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>Centre Hospitalier Régional (C.H.R.)</t>
+  </si>
+  <si>
+    <t>292</t>
+  </si>
+  <si>
+    <t>Centre Hospitalier Spécialisé lutte Maladies Mentales</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>Centre hospitalier, ex Hôpital local</t>
+  </si>
+  <si>
+    <t>214</t>
+  </si>
+  <si>
+    <t>Centre Hébergement &amp; Réinsertion Sociale (C.H.R.S.)</t>
+  </si>
+  <si>
+    <t>363</t>
+  </si>
+  <si>
+    <t>Centre moyen et long séjour</t>
+  </si>
+  <si>
+    <t>189</t>
+  </si>
+  <si>
+    <t>Centre Médico-Psycho-Pédagogique (C.M.P.P.)</t>
+  </si>
+  <si>
+    <t>156</t>
+  </si>
+  <si>
+    <t>Centre Médico-Psychologique (C.M.P.)</t>
+  </si>
+  <si>
+    <t>268</t>
+  </si>
+  <si>
+    <t>Centre Médico-Scolaire</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>Centre Parental</t>
+  </si>
+  <si>
+    <t>166</t>
+  </si>
+  <si>
+    <t>Centre Parents-Enfants de moins de 3 ans</t>
+  </si>
+  <si>
+    <t>430</t>
+  </si>
+  <si>
+    <t>Centre Postcure Malades Mentaux</t>
+  </si>
+  <si>
+    <t>431</t>
+  </si>
+  <si>
+    <t>Centre Postcure pour Alcooliques</t>
+  </si>
+  <si>
+    <t>432</t>
+  </si>
+  <si>
+    <t>Centre Postcure pour Toxicomanes</t>
+  </si>
+  <si>
+    <t>442</t>
+  </si>
+  <si>
+    <t>Centre Provisoire Hébergement (C.P.H.)</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>Centre Réentrainement au travail</t>
+  </si>
+  <si>
+    <t>322</t>
+  </si>
+  <si>
+    <t>Centre Rég.Informatiq.Hospit.</t>
+  </si>
+  <si>
+    <t>439</t>
+  </si>
+  <si>
+    <t>Centre Santé Polyvalent</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>Centre Social</t>
+  </si>
+  <si>
+    <t>197</t>
+  </si>
+  <si>
+    <t>Centre soins accompagnement prévention addictologie (CSAPA)</t>
+  </si>
+  <si>
+    <t>285</t>
+  </si>
+  <si>
+    <t>Centres de Loisirs sans Hébergement</t>
+  </si>
+  <si>
+    <t>461</t>
+  </si>
+  <si>
+    <t>Centres de Ressources S.A.I. (Sans Aucune Indication)</t>
+  </si>
+  <si>
+    <t>463</t>
+  </si>
+  <si>
+    <t>Centres Locaux Information Coordination P.A.(C.L.I.C.)</t>
+  </si>
+  <si>
+    <t>217</t>
+  </si>
+  <si>
+    <t>Cité de Transit</t>
+  </si>
+  <si>
+    <t>375</t>
+  </si>
+  <si>
+    <t>Classe d'Adaptation</t>
+  </si>
+  <si>
+    <t>376</t>
+  </si>
+  <si>
+    <t>Classe Spéciale Ecole Primaire</t>
+  </si>
+  <si>
+    <t>434</t>
+  </si>
+  <si>
+    <t>Classe Spéciale en Ecole Maternelle</t>
+  </si>
+  <si>
+    <t>604</t>
+  </si>
+  <si>
+    <t>Communauté Professionnelle Territoriale de Santé (CPTS)</t>
+  </si>
+  <si>
+    <t>229</t>
+  </si>
+  <si>
+    <t>Consultation Problèmes naissance</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>Consultations de Nourrissons</t>
+  </si>
+  <si>
+    <t>167</t>
+  </si>
+  <si>
+    <t>Crèche Collective</t>
+  </si>
+  <si>
+    <t>169</t>
+  </si>
+  <si>
+    <t>Crèche Multi Accueil Collectif et Familial</t>
+  </si>
+  <si>
+    <t>398</t>
+  </si>
+  <si>
+    <t>Crèche Parentale</t>
+  </si>
+  <si>
+    <t>178</t>
+  </si>
+  <si>
+    <t>Ctre.Accueil- Accomp.Réduc.Risq.Usag. Drogues (C.A.A.R.U.D.)</t>
+  </si>
+  <si>
+    <t>261</t>
+  </si>
+  <si>
+    <t>D.D.A.S.S.</t>
+  </si>
+  <si>
+    <t>401</t>
+  </si>
+  <si>
+    <t>D.R.A.S.S.</t>
+  </si>
+  <si>
+    <t>267</t>
+  </si>
+  <si>
+    <t>Dispensaire Antihansénien</t>
+  </si>
+  <si>
+    <t>142</t>
+  </si>
+  <si>
+    <t>Dispensaire Antituberculeux</t>
+  </si>
+  <si>
+    <t>266</t>
+  </si>
+  <si>
+    <t>Dispensaire Antivénérien</t>
+  </si>
+  <si>
+    <t>297</t>
+  </si>
+  <si>
+    <t>Dispensaire Polyvalent</t>
+  </si>
+  <si>
+    <t>606</t>
+  </si>
+  <si>
+    <t>Dispositif d'appui à la coordination (DAC)</t>
+  </si>
+  <si>
+    <t>614</t>
+  </si>
+  <si>
+    <t>Dispositif Spécifique Régional du Cancer (DSRC)</t>
+  </si>
+  <si>
+    <t>650</t>
+  </si>
+  <si>
+    <t>Dispositifs Spécifiques Régionaux en périnatalité</t>
+  </si>
+  <si>
+    <t>316</t>
+  </si>
+  <si>
+    <t>Ecole d'aides médico-psychologiques</t>
+  </si>
+  <si>
+    <t>272</t>
+  </si>
+  <si>
+    <t>Ecole d'ambulanciers</t>
+  </si>
+  <si>
+    <t>317</t>
+  </si>
+  <si>
+    <t>Ecole d'animateurs socio-éducatifs</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>Ecole d'ergothérapeutes</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>Ecole d'infirmiers anesthésistes</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>Ecole d'infirmiers de bloc opératoire</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>Ecole d'éducateurs de jeunes enfants</t>
+  </si>
+  <si>
+    <t>280</t>
+  </si>
+  <si>
+    <t>Ecole d'éducateurs spécialisés</t>
+  </si>
+  <si>
+    <t>314</t>
+  </si>
+  <si>
+    <t>Ecole d'éducateurs techniques spécialisés</t>
+  </si>
+  <si>
+    <t>326</t>
+  </si>
+  <si>
+    <t>Ecole de cadres</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de manipulateurs d'électro-radiologie</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de masseurs-kinésithérapeutes</t>
+  </si>
+  <si>
+    <t>349</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de sages-femmes</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>Ecole de cadres de secteur psychiatrique</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>Ecole de cadres infirmiers</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>Ecole de conseillers en économie sociale et familiale</t>
+  </si>
+  <si>
+    <t>276</t>
+  </si>
+  <si>
+    <t>Ecole de laborantins d'analyses médicales</t>
+  </si>
+  <si>
+    <t>283</t>
+  </si>
+  <si>
+    <t>Ecole de manipulateurs d'électro-radiologie</t>
+  </si>
+  <si>
+    <t>275</t>
+  </si>
+  <si>
+    <t>Ecole de masseurs-kinésithérapeutes</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>Ecole de moniteurs-éducateurs</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>Ecole de psycho-motriciens</t>
+  </si>
+  <si>
+    <t>282</t>
+  </si>
+  <si>
+    <t>Ecole de pédicures-podologues</t>
+  </si>
+  <si>
+    <t>277</t>
+  </si>
+  <si>
+    <t>Ecole de péricultrices</t>
+  </si>
+  <si>
+    <t>274</t>
+  </si>
+  <si>
+    <t>Ecole de sages_femmes</t>
+  </si>
+  <si>
+    <t>279</t>
+  </si>
+  <si>
+    <t>Ecole de service social</t>
+  </si>
+  <si>
+    <t>284</t>
+  </si>
+  <si>
+    <t>Ecole de travailleuses familiales</t>
+  </si>
+  <si>
+    <t>423</t>
+  </si>
+  <si>
+    <t>Ecole des cadres de laborantins d'analyses médicales</t>
+  </si>
+  <si>
+    <t>374</t>
+  </si>
+  <si>
+    <t>Ecole Nationale Santé Publique (E.N.S.P.)</t>
+  </si>
+  <si>
+    <t>386</t>
+  </si>
+  <si>
+    <t>Ecole Secondaire Spéciale</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>Ecoles Formant aux Professions Sanitaires</t>
+  </si>
+  <si>
+    <t>436</t>
+  </si>
+  <si>
+    <t>Ecoles Formant aux Professions Sanitaires et Sociales</t>
+  </si>
+  <si>
+    <t>330</t>
+  </si>
+  <si>
+    <t>Ecoles Formant aux Professions Sociales</t>
+  </si>
+  <si>
+    <t>502</t>
+  </si>
+  <si>
+    <t>EHPA ne percevant pas des crédits d'assurance maladie</t>
+  </si>
+  <si>
+    <t>501</t>
+  </si>
+  <si>
+    <t>EHPA percevant des crédits d'assurance maladie</t>
+  </si>
+  <si>
+    <t>699</t>
+  </si>
+  <si>
+    <t>Entité Ayant Autorisation</t>
+  </si>
+  <si>
+    <t>247</t>
+  </si>
+  <si>
+    <t>Entreprise adaptée</t>
+  </si>
+  <si>
+    <t>420</t>
+  </si>
+  <si>
+    <t>Entreprise d'Insertion</t>
+  </si>
+  <si>
+    <t>447</t>
+  </si>
+  <si>
+    <t>Entreprise Intérim Insertion</t>
+  </si>
+  <si>
+    <t>647</t>
+  </si>
+  <si>
+    <t>Equipe de Soins Spécialisés</t>
+  </si>
+  <si>
+    <t>608</t>
+  </si>
+  <si>
+    <t>Equipe mobile médico-sociale précarité (EMMSP)</t>
+  </si>
+  <si>
+    <t>343</t>
+  </si>
+  <si>
+    <t>Equipe Préparation et Suite Reclassement (EPSR)</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>Espaces de vie affective, relationnelle et sexuelle (EVARS)</t>
+  </si>
+  <si>
+    <t>644</t>
+  </si>
+  <si>
+    <t>Etab. de mise à l'abri pour les pers. se déclarant mineures non accompagnées</t>
+  </si>
+  <si>
+    <t>448</t>
+  </si>
+  <si>
+    <t>Etab.Acc.Médicalisé en tout ou partie personnes handicapées</t>
+  </si>
+  <si>
+    <t>449</t>
+  </si>
+  <si>
+    <t>Etab.Accueil Non Médicalisé pour personnes handicapées</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>Etablissement Acc.Collect.Parental Régulier &amp; Occasionnel</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>Etablissement Consultation Protection Infantile</t>
+  </si>
+  <si>
+    <t>174</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Collectif Régulier et Occasionnel</t>
+  </si>
+  <si>
+    <t>390</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Temporaire d'Enfants Handicapés</t>
+  </si>
+  <si>
+    <t>395</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Temporaire pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>394</t>
+  </si>
+  <si>
+    <t>Etablissement d'Accueil Temporaire pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>Etablissement d'hébergement pour personnes âgées dépendantes</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>Etablissement de Consultation Pré et Post-natale</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>Etablissement de Convalescence et de Repos</t>
+  </si>
+  <si>
+    <t>690</t>
+  </si>
+  <si>
+    <t>Etablissement de Fabrication Annexe à une Officine</t>
+  </si>
+  <si>
+    <t>278</t>
+  </si>
+  <si>
+    <t>Etablissement de formation polyvalent</t>
+  </si>
+  <si>
+    <t>144</t>
+  </si>
+  <si>
+    <t>Etablissement de Lutte Contre la Tuberculose</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>Etablissement de santé privé autorisé en SSR</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Chirurgicaux</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins du Service de Santé des Armées</t>
+  </si>
+  <si>
+    <t>362</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Longue Durée</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Médicaux</t>
+  </si>
+  <si>
+    <t>365</t>
+  </si>
+  <si>
+    <t>Etablissement de Soins Pluridisciplinaire</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>Etablissement de Transfusion Sanguine</t>
+  </si>
+  <si>
+    <t>246</t>
+  </si>
+  <si>
+    <t>Etablissement et Service d'Aide par le Travail (E.S.A.T.)</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental Autres Adultes</t>
+  </si>
+  <si>
+    <t>378</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental Enfance Protégée</t>
+  </si>
+  <si>
+    <t>379</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>377</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental pour Enfance Handicapée</t>
+  </si>
+  <si>
+    <t>381</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental pour Personnes Agées</t>
+  </si>
+  <si>
+    <t>370</t>
+  </si>
+  <si>
+    <t>Etablissement Expérimental pour personnes handicapées</t>
+  </si>
+  <si>
+    <t>191</t>
+  </si>
+  <si>
+    <t>Etablissement pour Déficients Moteurs Cérébraux</t>
+  </si>
+  <si>
+    <t>193</t>
+  </si>
+  <si>
+    <t>Etablissement pour Déficients Moteurs et Moteurs Cérébraux</t>
+  </si>
+  <si>
+    <t>188</t>
+  </si>
+  <si>
+    <t>Etablissement pour Enfants ou Adolescents Polyhandicapés</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>Etablissement Réadaptation Fonctionnelle</t>
+  </si>
+  <si>
+    <t>262</t>
+  </si>
+  <si>
+    <t>Etablissement Régional d'Enseignement Adapté</t>
+  </si>
+  <si>
+    <t>433</t>
+  </si>
+  <si>
+    <t>Etablissement Sanitaire des Prisons</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>Etablissement Soins Obstétriques Chirurgico-Gynécologiques</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>Etablissement Thermal</t>
+  </si>
+  <si>
+    <t>164</t>
+  </si>
+  <si>
+    <t>Etablissements Expérimentaux Accueil de la Petite Enfance</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>Foyer Club Restaurant</t>
+  </si>
+  <si>
+    <t>437</t>
+  </si>
+  <si>
+    <t>Foyer d'Accueil Médicalisé pour Adultes Handicapés (F.A.M.)</t>
+  </si>
+  <si>
+    <t>253</t>
+  </si>
+  <si>
+    <t>Foyer d'Accueil Polyvalent pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>Foyer de l'Enfance</t>
+  </si>
+  <si>
+    <t>382</t>
+  </si>
+  <si>
+    <t>Foyer de Vie pour Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>252</t>
+  </si>
+  <si>
+    <t>Foyer Hébergement Adultes Handicapés</t>
+  </si>
+  <si>
+    <t>396</t>
+  </si>
+  <si>
+    <t>Foyer Hébergement Enfants et Adolescents Handicapés</t>
+  </si>
+  <si>
+    <t>256</t>
+  </si>
+  <si>
+    <t>Foyer Travailleurs Migrants non transformé en Résidence Soc.</t>
+  </si>
+  <si>
+    <t>257</t>
+  </si>
+  <si>
+    <t>Foyers de jeunes travailleurs</t>
+  </si>
+  <si>
+    <t>171</t>
+  </si>
+  <si>
+    <t>Garderie et Jardin d'Enfants</t>
+  </si>
+  <si>
+    <t>697</t>
+  </si>
+  <si>
+    <t>Groupement de coopération sanitaire - Etablissement de santé</t>
+  </si>
+  <si>
+    <t>696</t>
+  </si>
+  <si>
+    <t>Groupement de coopération sanitaire de moyens</t>
+  </si>
+  <si>
+    <t>695</t>
+  </si>
+  <si>
+    <t>Groupement de coopération sanitaire de moyens - Exploitant</t>
+  </si>
+  <si>
+    <t>607</t>
+  </si>
+  <si>
+    <t>Groupement Régional d'Appui au Développement de la e-Santé (GRADeS)</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>Halte Garderie</t>
+  </si>
+  <si>
+    <t>399</t>
+  </si>
+  <si>
+    <t>Halte Garderie Parentale</t>
+  </si>
+  <si>
+    <t>623</t>
+  </si>
+  <si>
+    <t>Herboristerie</t>
+  </si>
+  <si>
+    <t>199</t>
+  </si>
+  <si>
+    <t>Hospice</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>Hospitalisation à Domicile</t>
+  </si>
+  <si>
+    <t>353</t>
+  </si>
+  <si>
+    <t>Hôpital de Jour Spécialités Médicales</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>Hôpital des armées</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>Inst. régional de formation des travailleurs sociaux</t>
+  </si>
+  <si>
+    <t>630</t>
+  </si>
+  <si>
+    <t>Installation autonome de chirurgie esthétique</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>Institut d'Education Sensorielle Sourd-Aveugle</t>
+  </si>
+  <si>
+    <t>192</t>
+  </si>
+  <si>
+    <t>Institut d'éducation motrice</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>Institut de formation en soins infirmiers (I.F.S.I.)</t>
+  </si>
+  <si>
+    <t>183</t>
+  </si>
+  <si>
+    <t>Institut Médico-Educatif (I.M.E.)</t>
+  </si>
+  <si>
+    <t>185</t>
+  </si>
+  <si>
+    <t>Institut Médico-Professionnel (I.M.Pro.)</t>
+  </si>
+  <si>
+    <t>184</t>
+  </si>
+  <si>
+    <t>Institut Médico-Pédagogique (I.M.P.)</t>
+  </si>
+  <si>
+    <t>195</t>
+  </si>
+  <si>
+    <t>Institut pour Déficients Auditifs</t>
+  </si>
+  <si>
+    <t>194</t>
+  </si>
+  <si>
+    <t>Institut pour Déficients Visuels</t>
+  </si>
+  <si>
+    <t>186</t>
+  </si>
+  <si>
+    <t>Institut Thérapeutique Éducatif et Pédagogique (I.T.E.P.)</t>
+  </si>
+  <si>
+    <t>411</t>
+  </si>
+  <si>
+    <t>Intermédiaire de Placement Social</t>
+  </si>
+  <si>
+    <t>402</t>
+  </si>
+  <si>
+    <t>Jardin d'Enfants Spécialisé</t>
+  </si>
+  <si>
+    <t>610</t>
+  </si>
+  <si>
+    <t>Laboratoire d'Analyses</t>
+  </si>
+  <si>
+    <t>611</t>
+  </si>
+  <si>
+    <t>Laboratoire de Biologie Médicale</t>
+  </si>
+  <si>
+    <t>624</t>
+  </si>
+  <si>
+    <t>Laboratoire pharmaceutique préparant délivrant allergènes</t>
+  </si>
+  <si>
+    <t>233</t>
+  </si>
+  <si>
+    <t>Lactarium</t>
+  </si>
+  <si>
+    <t>617</t>
+  </si>
+  <si>
+    <t>Lieu de soins non programmés</t>
+  </si>
+  <si>
+    <t>462</t>
+  </si>
+  <si>
+    <t>Lieux de Vie et d’Accueil</t>
+  </si>
+  <si>
+    <t>213</t>
+  </si>
+  <si>
+    <t>Lits d'Accueil Médicalisés (L.A.M.)</t>
+  </si>
+  <si>
+    <t>180</t>
+  </si>
+  <si>
+    <t>Lits Halte Soins Santé (L.H.S.S.)</t>
+  </si>
+  <si>
+    <t>324</t>
+  </si>
+  <si>
+    <t>Logement Foyer non Spécialisé</t>
+  </si>
+  <si>
+    <t>621</t>
+  </si>
+  <si>
+    <t>Lunetterie Médicale</t>
+  </si>
+  <si>
+    <t>271</t>
+  </si>
+  <si>
+    <t>Maison d'accueil Hospitalière</t>
+  </si>
+  <si>
+    <t>255</t>
+  </si>
+  <si>
+    <t>Maison d'Accueil Spécialisée (M.A.S.)</t>
+  </si>
+  <si>
+    <t>367</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants non Conventionnée ni Habilitée</t>
+  </si>
+  <si>
+    <t>179</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants à Caractère Sanitaire Permanente</t>
+  </si>
+  <si>
+    <t>163</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants à Caractère Sanitaire Temporaire</t>
+  </si>
+  <si>
+    <t>177</t>
+  </si>
+  <si>
+    <t>Maison d'Enfants à Caractère Social</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>Maison de Retraite</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>Maison de Régime</t>
+  </si>
+  <si>
+    <t>603</t>
+  </si>
+  <si>
+    <t>Maison de santé (L.6223-3)</t>
+  </si>
+  <si>
+    <t>161</t>
+  </si>
+  <si>
+    <t>Maison de Santé pour Maladies Mentales</t>
+  </si>
+  <si>
+    <t>609</t>
+  </si>
+  <si>
+    <t>Maison Départementale pour Personnes Handicapées (MDPH)</t>
+  </si>
+  <si>
+    <t>181</t>
+  </si>
+  <si>
+    <t>Maison Familiale de Vacances</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>Maison Relai</t>
+  </si>
+  <si>
+    <t>251</t>
+  </si>
+  <si>
+    <t>Maison Vacances pour Handicapés</t>
+  </si>
+  <si>
+    <t>631</t>
+  </si>
+  <si>
+    <t>Maisons de naissance</t>
+  </si>
+  <si>
+    <t>258</t>
+  </si>
+  <si>
+    <t>Maisons Relais - Pensions de Famille</t>
+  </si>
+  <si>
+    <t>620</t>
+  </si>
+  <si>
+    <t>Pharmacie d'Officine</t>
+  </si>
+  <si>
+    <t>628</t>
+  </si>
+  <si>
+    <t>Pharmacie Minière</t>
+  </si>
+  <si>
+    <t>629</t>
+  </si>
+  <si>
+    <t>Pharmacie Mutualiste</t>
+  </si>
+  <si>
+    <t>173</t>
+  </si>
+  <si>
+    <t>Pouponnière à Caractère Sanitaire</t>
+  </si>
+  <si>
+    <t>172</t>
+  </si>
+  <si>
+    <t>Pouponnière à Caractère Social</t>
+  </si>
+  <si>
+    <t>627</t>
+  </si>
+  <si>
+    <t>Propharmacie</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>Protection Maternelle et Infantile (P.M.I.)</t>
+  </si>
+  <si>
+    <t>452</t>
+  </si>
+  <si>
+    <t>Régie de Quartier</t>
+  </si>
+  <si>
+    <t>216</t>
+  </si>
+  <si>
+    <t>Résidence Hôtelière à Vocation Sociale (R.H.V.S)</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>Résidences autonomie</t>
+  </si>
+  <si>
+    <t>320</t>
+  </si>
+  <si>
+    <t>S.A.M.U. et Centre 15</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>Section Education Spéciale Classe Atelier</t>
+  </si>
+  <si>
+    <t>329</t>
+  </si>
+  <si>
+    <t>Sectorisation Psychiatrique</t>
+  </si>
+  <si>
+    <t>643</t>
+  </si>
+  <si>
+    <t>Serv. d'éval de la minorité de l'isolement pour les pers. se déclarant mineures</t>
+  </si>
+  <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>Service Accueil Familial pour la Petite Enfance</t>
+  </si>
+  <si>
+    <t>371</t>
+  </si>
+  <si>
+    <t>Service Action Socio-Educative pour Familles en difficulté</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>Service AEMO et AED</t>
+  </si>
+  <si>
+    <t>460</t>
+  </si>
+  <si>
+    <t>Service autonomie aide (SAA)</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>Service autonomie aide et soins (SAAS)</t>
+  </si>
+  <si>
+    <t>397</t>
+  </si>
+  <si>
+    <t>Service Auxiliaire de Vie pour Handicapés</t>
+  </si>
+  <si>
+    <t>445</t>
+  </si>
+  <si>
+    <t>Service d'accompagnement médico-social adultes handicapés</t>
+  </si>
+  <si>
+    <t>446</t>
+  </si>
+  <si>
+    <t>Service d'Accompagnement à la Vie Sociale (S.A.V.S.)</t>
+  </si>
+  <si>
+    <t>451</t>
+  </si>
+  <si>
+    <t>Service d'Aide aux Familles en Difficulté</t>
+  </si>
+  <si>
+    <t>450</t>
+  </si>
+  <si>
+    <t>Service d'Aide aux Personnes Agées</t>
+  </si>
+  <si>
+    <t>640</t>
+  </si>
+  <si>
+    <t>Service d'aide et d'accompagnement à domicile aux familles (SAADF)</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>Service d'Aide Ménagère à Domicile</t>
+  </si>
+  <si>
+    <t>327</t>
+  </si>
+  <si>
+    <t>Service d'Ambulances</t>
+  </si>
+  <si>
+    <t>418</t>
+  </si>
+  <si>
+    <t>Service d'Enquêtes Sociales (S.E.S.)</t>
+  </si>
+  <si>
+    <t>342</t>
+  </si>
+  <si>
+    <t>Service d'information et de soutien aux tuteurs familiaux</t>
+  </si>
+  <si>
+    <t>182</t>
+  </si>
+  <si>
+    <t>Service d'Éducation Spéciale et de Soins à Domicile</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>Service de placement familial</t>
+  </si>
+  <si>
+    <t>286</t>
+  </si>
+  <si>
+    <t>Service de prévention spécialisée</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>Service de Repas à Domicile</t>
+  </si>
+  <si>
+    <t>453</t>
+  </si>
+  <si>
+    <t>Service de Réparation Pénale</t>
+  </si>
+  <si>
+    <t>354</t>
+  </si>
+  <si>
+    <t>Service de Soins Infirmiers A Domicile (S.S.I.A.D)</t>
+  </si>
+  <si>
+    <t>346</t>
+  </si>
+  <si>
+    <t>Service de Travailleuses Familiales</t>
+  </si>
+  <si>
+    <t>341</t>
+  </si>
+  <si>
+    <t>Service dédié mesures d'accompagnement social personnalisé</t>
+  </si>
+  <si>
+    <t>344</t>
+  </si>
+  <si>
+    <t>Service délégué aux prestations familiales</t>
+  </si>
+  <si>
+    <t>242</t>
+  </si>
+  <si>
+    <t>Service d’Activité de Jour</t>
+  </si>
+  <si>
+    <t>441</t>
+  </si>
+  <si>
+    <t>Service d’Intervention Educative en Milieu Ouvert</t>
+  </si>
+  <si>
+    <t>440</t>
+  </si>
+  <si>
+    <t>Service d’Investigation Educative</t>
+  </si>
+  <si>
+    <t>427</t>
+  </si>
+  <si>
+    <t>Service Educatif Auprès des Tribunaux (S.E.A.T.)</t>
+  </si>
+  <si>
+    <t>340</t>
+  </si>
+  <si>
+    <t>Service mandataire judiciaire à la protection des majeurs</t>
+  </si>
+  <si>
+    <t>415</t>
+  </si>
+  <si>
+    <t>Service Médico-Psychologique Régional (S.M.P.R.)</t>
+  </si>
+  <si>
+    <t>405</t>
+  </si>
+  <si>
+    <t>Service Social Polyvalent de Secteur</t>
+  </si>
+  <si>
+    <t>403</t>
+  </si>
+  <si>
+    <t>Service Social Spécialisé ou Polyvalent de Catégorie</t>
+  </si>
+  <si>
+    <t>345</t>
+  </si>
+  <si>
+    <t>Service Tutelle Prestation Sociale</t>
+  </si>
+  <si>
+    <t>616</t>
+  </si>
+  <si>
+    <t>Services de Prévention et de Santé au Travail (SPST)</t>
+  </si>
+  <si>
+    <t>642</t>
+  </si>
+  <si>
+    <t>Services départementaux d'incendie et de secours</t>
+  </si>
+  <si>
+    <t>639</t>
+  </si>
+  <si>
+    <t>Sociétés de téléconsultation (STLC)</t>
+  </si>
+  <si>
+    <t>146</t>
+  </si>
+  <si>
+    <t>Structure d'Alternative à la dialyse en centre</t>
+  </si>
+  <si>
+    <t>632</t>
+  </si>
+  <si>
+    <t>Structure Dispensatrice à domicile d'Oxygène à usage médical</t>
+  </si>
+  <si>
+    <t>633</t>
+  </si>
+  <si>
+    <t>Structure Expérimentale en Santé</t>
+  </si>
+  <si>
+    <t>648</t>
+  </si>
+  <si>
+    <t>Structure qui contribue au Service d'Accès aux Soins</t>
+  </si>
+  <si>
+    <t>426</t>
+  </si>
+  <si>
+    <t>Syndicat Inter Hospitalier (S.I.H.)</t>
+  </si>
+  <si>
+    <t>422</t>
+  </si>
+  <si>
+    <t>Traitements Spécialisés à Domicile</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>Unité Mobile Hospitalière</t>
+  </si>
+  <si>
+    <t>464</t>
+  </si>
+  <si>
+    <t>Unités Evaluation Réentraînement et d'Orient. Soc. et Pro.</t>
+  </si>
+  <si>
+    <t>176</t>
+  </si>
+  <si>
+    <t>Village d'Enfants</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>Établissement de Placement</t>
+  </si>
+  <si>
+    <t>198</t>
+  </si>
+  <si>
+    <t>Établissement et Service de Préorientation</t>
+  </si>
+  <si>
+    <t>249</t>
+  </si>
+  <si>
+    <t>Établissement et Service de Réadaptation Professionnelle</t>
   </si>
 </sst>
 </file>
@@ -488,4 +2413,6686 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G316"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>42</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>40</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>43</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>44</v>
+      </c>
+      <c r="F1" t="s" s="1">
+        <v>45</v>
+      </c>
+      <c r="G1" t="s" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="F2" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="F4" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="F5" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="F6" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="E9" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="F10" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="F11" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="F12" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G12" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G13" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="F14" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G14" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="F15" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="F16" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="F17" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E18" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="F18" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="E20" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="F20" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="E21" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="F21" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="E22" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="F22" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="E23" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="F23" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="E24" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="E25" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="E26" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="F26" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="E27" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="F27" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="E28" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F28" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="E29" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="F29" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="E31" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="F31" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="E32" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="F32" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E33" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F33" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="E34" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="F34" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="E35" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="E36" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F36" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="E37" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="F37" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="E38" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="F38" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="E39" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="F39" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="E40" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="F40" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F41" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="E42" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="E43" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E44" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="E45" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="E46" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="F46" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="E47" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="F47" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="E48" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="F48" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="E49" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="F49" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="E50" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="F50" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E51" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="F51" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E52" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="F52" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="E53" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="F53" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="E54" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="F54" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="E55" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="F55" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="E56" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="F56" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="E57" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="F57" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="E58" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="F58" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="E59" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="F59" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E60" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="F60" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="E61" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="F61" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="E62" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="F62" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="E63" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="F63" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="E64" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="F64" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="E65" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="F65" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="E66" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="F66" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="E67" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="F67" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="E68" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="F68" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="E69" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="F69" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="E70" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="F70" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="E71" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="F71" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="E72" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="F72" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="E73" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="F73" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="E74" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="F74" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="E75" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="F75" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="E76" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="F76" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="E77" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="F77" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="E78" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="F78" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="E79" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="F79" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="E80" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="F80" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="E81" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="F81" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="E82" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="F82" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="E83" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="F83" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="E84" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="F84" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="E85" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="F85" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="E86" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="F86" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="E87" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="F87" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="E88" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="F88" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="E89" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="F89" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="E90" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="F90" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="E91" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="F91" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="E92" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="F92" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="E93" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="F93" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="E94" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="F94" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="E95" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="F95" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="E96" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="F96" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="E97" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="F97" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="E98" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="F98" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="E99" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="F99" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="E100" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="F100" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="E101" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="F101" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="E102" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="F102" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="E103" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="F103" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="E104" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="F104" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="E105" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="F105" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="E106" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="F106" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="E107" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="F107" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="E108" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="F108" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="E109" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="F109" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="E110" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="F110" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="E111" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="F111" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="E112" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="F112" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="E113" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="F113" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="E114" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="F114" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="E115" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="F115" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="E116" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="F116" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="E117" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="F117" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="E118" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="F118" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="E119" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="F119" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="E120" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="F120" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="E121" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="F121" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="E122" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="F122" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="E123" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="F123" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="E124" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="F124" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C125" s="2"/>
+      <c r="D125" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="E125" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="F125" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G125" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C126" s="2"/>
+      <c r="D126" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="E126" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="F126" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G126" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C127" s="2"/>
+      <c r="D127" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="E127" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="F127" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G127" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="E128" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="F128" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="E129" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="F129" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="E130" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="F130" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="E131" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="F131" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="E132" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="F132" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="E133" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="F133" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="E134" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="F134" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="E135" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="F135" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="E136" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="F136" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="E137" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="F137" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="E138" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="F138" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="E139" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="F139" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="E140" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="F140" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G140" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="E141" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="F141" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G141" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="E142" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="F142" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G142" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C143" s="2"/>
+      <c r="D143" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="E143" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="F143" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G143" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="E144" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="F144" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G144" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="E145" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="F145" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="E146" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="F146" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G146" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="E147" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="F147" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G147" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="D148" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="E148" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="F148" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G148" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C149" s="2"/>
+      <c r="D149" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="E149" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="F149" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G149" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C150" s="2"/>
+      <c r="D150" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="E150" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="F150" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G150" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C151" s="2"/>
+      <c r="D151" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="E151" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="F151" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G151" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="D152" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="E152" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="F152" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G152" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C153" s="2"/>
+      <c r="D153" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="E153" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="F153" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G153" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C154" s="2"/>
+      <c r="D154" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="E154" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="F154" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G154" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C155" s="2"/>
+      <c r="D155" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="E155" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="F155" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G155" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C156" s="2"/>
+      <c r="D156" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="E156" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="F156" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G156" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C157" s="2"/>
+      <c r="D157" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="E157" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="F157" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G157" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C158" s="2"/>
+      <c r="D158" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="E158" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="F158" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G158" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C159" s="2"/>
+      <c r="D159" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="E159" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="F159" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G159" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C160" s="2"/>
+      <c r="D160" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="E160" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="F160" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G160" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C161" s="2"/>
+      <c r="D161" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="E161" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="F161" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G161" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C162" s="2"/>
+      <c r="D162" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="E162" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="F162" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G162" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C163" s="2"/>
+      <c r="D163" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="E163" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="F163" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G163" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B164" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C164" s="2"/>
+      <c r="D164" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="E164" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="F164" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G164" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C165" s="2"/>
+      <c r="D165" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="E165" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="F165" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G165" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C166" s="2"/>
+      <c r="D166" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="E166" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="F166" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G166" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C167" s="2"/>
+      <c r="D167" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="E167" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="F167" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G167" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C168" s="2"/>
+      <c r="D168" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="E168" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="F168" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G168" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C169" s="2"/>
+      <c r="D169" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="E169" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="F169" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G169" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C170" s="2"/>
+      <c r="D170" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="E170" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="F170" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G170" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C171" s="2"/>
+      <c r="D171" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="E171" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="F171" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G171" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C172" s="2"/>
+      <c r="D172" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="E172" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="F172" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G172" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B173" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C173" s="2"/>
+      <c r="D173" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="E173" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="F173" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G173" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B174" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C174" s="2"/>
+      <c r="D174" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="E174" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="F174" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G174" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B175" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C175" s="2"/>
+      <c r="D175" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="E175" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="F175" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G175" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B176" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C176" s="2"/>
+      <c r="D176" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="E176" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="F176" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G176" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B177" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C177" s="2"/>
+      <c r="D177" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="E177" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="F177" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G177" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B178" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C178" s="2"/>
+      <c r="D178" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="E178" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="F178" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G178" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B179" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C179" s="2"/>
+      <c r="D179" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="E179" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="F179" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G179" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B180" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C180" s="2"/>
+      <c r="D180" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="E180" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="F180" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G180" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B181" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C181" s="2"/>
+      <c r="D181" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="E181" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="F181" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G181" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B182" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C182" s="2"/>
+      <c r="D182" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="E182" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="F182" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G182" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B183" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C183" s="2"/>
+      <c r="D183" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="E183" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="F183" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G183" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B184" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C184" s="2"/>
+      <c r="D184" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="E184" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="F184" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G184" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B185" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C185" s="2"/>
+      <c r="D185" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="E185" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="F185" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G185" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B186" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C186" s="2"/>
+      <c r="D186" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="E186" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="F186" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G186" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C187" s="2"/>
+      <c r="D187" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="E187" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="F187" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G187" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B188" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C188" s="2"/>
+      <c r="D188" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="E188" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="F188" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G188" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C189" s="2"/>
+      <c r="D189" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="E189" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="F189" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G189" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B190" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C190" s="2"/>
+      <c r="D190" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="E190" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="F190" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G190" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B191" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C191" s="2"/>
+      <c r="D191" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="E191" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="F191" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G191" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B192" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C192" s="2"/>
+      <c r="D192" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="E192" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="F192" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G192" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B193" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C193" s="2"/>
+      <c r="D193" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="E193" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="F193" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G193" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B194" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C194" s="2"/>
+      <c r="D194" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="E194" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="F194" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G194" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B195" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C195" s="2"/>
+      <c r="D195" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="E195" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="F195" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G195" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B196" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C196" s="2"/>
+      <c r="D196" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="E196" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="F196" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G196" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B197" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C197" s="2"/>
+      <c r="D197" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="E197" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="F197" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G197" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B198" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C198" s="2"/>
+      <c r="D198" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="E198" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="F198" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G198" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B199" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C199" s="2"/>
+      <c r="D199" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="E199" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="F199" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G199" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B200" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C200" s="2"/>
+      <c r="D200" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="E200" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="F200" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G200" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B201" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C201" s="2"/>
+      <c r="D201" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="E201" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="F201" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G201" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B202" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C202" s="2"/>
+      <c r="D202" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="E202" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="F202" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G202" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B203" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C203" s="2"/>
+      <c r="D203" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="E203" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="F203" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G203" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B204" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C204" s="2"/>
+      <c r="D204" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="E204" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="F204" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G204" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B205" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C205" s="2"/>
+      <c r="D205" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="E205" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="F205" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G205" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B206" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C206" s="2"/>
+      <c r="D206" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="E206" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="F206" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G206" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B207" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C207" s="2"/>
+      <c r="D207" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="E207" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="F207" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G207" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B208" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C208" s="2"/>
+      <c r="D208" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="E208" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="F208" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G208" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B209" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C209" s="2"/>
+      <c r="D209" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="E209" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="F209" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G209" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B210" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C210" s="2"/>
+      <c r="D210" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="E210" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="F210" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G210" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B211" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C211" s="2"/>
+      <c r="D211" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="E211" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="F211" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G211" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B212" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C212" s="2"/>
+      <c r="D212" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="E212" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="F212" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G212" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B213" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C213" s="2"/>
+      <c r="D213" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="E213" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="F213" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G213" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B214" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C214" s="2"/>
+      <c r="D214" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="E214" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="F214" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G214" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B215" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C215" s="2"/>
+      <c r="D215" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="E215" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="F215" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G215" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B216" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C216" s="2"/>
+      <c r="D216" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="E216" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="F216" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G216" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B217" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C217" s="2"/>
+      <c r="D217" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="E217" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="F217" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G217" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B218" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C218" s="2"/>
+      <c r="D218" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="E218" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="F218" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G218" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B219" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C219" s="2"/>
+      <c r="D219" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="E219" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="F219" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G219" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B220" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C220" s="2"/>
+      <c r="D220" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="E220" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="F220" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G220" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B221" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C221" s="2"/>
+      <c r="D221" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="E221" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="F221" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G221" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B222" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C222" s="2"/>
+      <c r="D222" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="E222" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="F222" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G222" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B223" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C223" s="2"/>
+      <c r="D223" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="E223" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="F223" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G223" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B224" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C224" s="2"/>
+      <c r="D224" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="E224" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="F224" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G224" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B225" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C225" s="2"/>
+      <c r="D225" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="E225" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="F225" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G225" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B226" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C226" s="2"/>
+      <c r="D226" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="E226" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="F226" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G226" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B227" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C227" s="2"/>
+      <c r="D227" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="E227" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="F227" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G227" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B228" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C228" s="2"/>
+      <c r="D228" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="E228" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="F228" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G228" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B229" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C229" s="2"/>
+      <c r="D229" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="E229" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="F229" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G229" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B230" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C230" s="2"/>
+      <c r="D230" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="E230" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="F230" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G230" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B231" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C231" s="2"/>
+      <c r="D231" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="E231" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="F231" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G231" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B232" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C232" s="2"/>
+      <c r="D232" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="E232" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="F232" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G232" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B233" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C233" s="2"/>
+      <c r="D233" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="E233" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="F233" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G233" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B234" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C234" s="2"/>
+      <c r="D234" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="E234" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="F234" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G234" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B235" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C235" s="2"/>
+      <c r="D235" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="E235" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="F235" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G235" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B236" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C236" s="2"/>
+      <c r="D236" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="E236" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="F236" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G236" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B237" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C237" s="2"/>
+      <c r="D237" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="E237" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="F237" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G237" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B238" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C238" s="2"/>
+      <c r="D238" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="E238" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="F238" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G238" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B239" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C239" s="2"/>
+      <c r="D239" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="E239" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="F239" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G239" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B240" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C240" s="2"/>
+      <c r="D240" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="E240" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="F240" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G240" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B241" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C241" s="2"/>
+      <c r="D241" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="E241" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="F241" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G241" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B242" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C242" s="2"/>
+      <c r="D242" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="E242" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="F242" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G242" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B243" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C243" s="2"/>
+      <c r="D243" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="E243" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="F243" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G243" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B244" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C244" s="2"/>
+      <c r="D244" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="E244" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="F244" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G244" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B245" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C245" s="2"/>
+      <c r="D245" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="E245" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="F245" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G245" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B246" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C246" s="2"/>
+      <c r="D246" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="E246" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="F246" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G246" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B247" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C247" s="2"/>
+      <c r="D247" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="E247" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="F247" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G247" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B248" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C248" s="2"/>
+      <c r="D248" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="E248" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="F248" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G248" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B249" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C249" s="2"/>
+      <c r="D249" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="E249" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="F249" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G249" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B250" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C250" s="2"/>
+      <c r="D250" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="E250" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="F250" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G250" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B251" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C251" s="2"/>
+      <c r="D251" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="E251" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="F251" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G251" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B252" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C252" s="2"/>
+      <c r="D252" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="E252" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="F252" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G252" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B253" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C253" s="2"/>
+      <c r="D253" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="E253" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="F253" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G253" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B254" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C254" s="2"/>
+      <c r="D254" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="E254" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="F254" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G254" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B255" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C255" s="2"/>
+      <c r="D255" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="E255" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="F255" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G255" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B256" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C256" s="2"/>
+      <c r="D256" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="E256" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="F256" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G256" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B257" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C257" s="2"/>
+      <c r="D257" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="E257" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="F257" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G257" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B258" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C258" s="2"/>
+      <c r="D258" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="E258" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="F258" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G258" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B259" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C259" s="2"/>
+      <c r="D259" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="E259" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="F259" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G259" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B260" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C260" s="2"/>
+      <c r="D260" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="E260" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="F260" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G260" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B261" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C261" s="2"/>
+      <c r="D261" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="E261" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="F261" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G261" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B262" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C262" s="2"/>
+      <c r="D262" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="E262" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="F262" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G262" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B263" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C263" s="2"/>
+      <c r="D263" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="E263" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="F263" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G263" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B264" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C264" s="2"/>
+      <c r="D264" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="E264" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="F264" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G264" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B265" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C265" s="2"/>
+      <c r="D265" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="E265" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="F265" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G265" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B266" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C266" s="2"/>
+      <c r="D266" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="E266" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="F266" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G266" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B267" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C267" s="2"/>
+      <c r="D267" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="E267" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="F267" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G267" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B268" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C268" s="2"/>
+      <c r="D268" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="E268" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="F268" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G268" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B269" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C269" s="2"/>
+      <c r="D269" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="E269" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="F269" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G269" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B270" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C270" s="2"/>
+      <c r="D270" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="E270" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="F270" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G270" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B271" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C271" s="2"/>
+      <c r="D271" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="E271" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="F271" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G271" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B272" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C272" s="2"/>
+      <c r="D272" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="E272" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="F272" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G272" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B273" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C273" s="2"/>
+      <c r="D273" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="E273" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="F273" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G273" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B274" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C274" s="2"/>
+      <c r="D274" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="E274" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="F274" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G274" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B275" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C275" s="2"/>
+      <c r="D275" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="E275" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="F275" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G275" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B276" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C276" s="2"/>
+      <c r="D276" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="E276" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="F276" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G276" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B277" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C277" s="2"/>
+      <c r="D277" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="E277" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="F277" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G277" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B278" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C278" s="2"/>
+      <c r="D278" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="E278" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="F278" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G278" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B279" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C279" s="2"/>
+      <c r="D279" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="E279" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="F279" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G279" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B280" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C280" s="2"/>
+      <c r="D280" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="E280" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="F280" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G280" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B281" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C281" s="2"/>
+      <c r="D281" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="E281" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="F281" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G281" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B282" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C282" s="2"/>
+      <c r="D282" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="E282" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="F282" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G282" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B283" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C283" s="2"/>
+      <c r="D283" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="E283" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="F283" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G283" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B284" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C284" s="2"/>
+      <c r="D284" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="E284" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="F284" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G284" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B285" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C285" s="2"/>
+      <c r="D285" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="E285" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="F285" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G285" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B286" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C286" s="2"/>
+      <c r="D286" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="E286" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="F286" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G286" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B287" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C287" s="2"/>
+      <c r="D287" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="E287" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="F287" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G287" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B288" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C288" s="2"/>
+      <c r="D288" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="E288" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="F288" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G288" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B289" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C289" s="2"/>
+      <c r="D289" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="E289" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="F289" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G289" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B290" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C290" s="2"/>
+      <c r="D290" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="E290" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="F290" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G290" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B291" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C291" s="2"/>
+      <c r="D291" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="E291" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="F291" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G291" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B292" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C292" s="2"/>
+      <c r="D292" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="E292" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="F292" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G292" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B293" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C293" s="2"/>
+      <c r="D293" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="E293" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="F293" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G293" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B294" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C294" s="2"/>
+      <c r="D294" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="E294" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="F294" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G294" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B295" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C295" s="2"/>
+      <c r="D295" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="E295" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="F295" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G295" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B296" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C296" s="2"/>
+      <c r="D296" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="E296" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="F296" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G296" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B297" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C297" s="2"/>
+      <c r="D297" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="E297" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="F297" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G297" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B298" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C298" s="2"/>
+      <c r="D298" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="E298" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="F298" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G298" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B299" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C299" s="2"/>
+      <c r="D299" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="E299" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="F299" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G299" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B300" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C300" s="2"/>
+      <c r="D300" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="E300" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="F300" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G300" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B301" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C301" s="2"/>
+      <c r="D301" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="E301" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="F301" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G301" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B302" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C302" s="2"/>
+      <c r="D302" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="E302" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="F302" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G302" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B303" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C303" s="2"/>
+      <c r="D303" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="E303" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="F303" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G303" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B304" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C304" s="2"/>
+      <c r="D304" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="E304" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="F304" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G304" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B305" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C305" s="2"/>
+      <c r="D305" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="E305" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="F305" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G305" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B306" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C306" s="2"/>
+      <c r="D306" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="E306" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="F306" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G306" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B307" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C307" s="2"/>
+      <c r="D307" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="E307" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="F307" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G307" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B308" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C308" s="2"/>
+      <c r="D308" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="E308" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="F308" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G308" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B309" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C309" s="2"/>
+      <c r="D309" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="E309" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="F309" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G309" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B310" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C310" s="2"/>
+      <c r="D310" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="E310" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="F310" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G310" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B311" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C311" s="2"/>
+      <c r="D311" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="E311" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="F311" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G311" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B312" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C312" s="2"/>
+      <c r="D312" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="E312" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="F312" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G312" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B313" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C313" s="2"/>
+      <c r="D313" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="E313" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="F313" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G313" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B314" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C314" s="2"/>
+      <c r="D314" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="E314" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="F314" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G314" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B315" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C315" s="2"/>
+      <c r="D315" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="E315" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="F315" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G315" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="B316" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="C316" s="2"/>
+      <c r="D316" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="E316" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="F316" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G316" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>